--- a/channels/food-convenience/research/theme-stock.xlsx
+++ b/channels/food-convenience/research/theme-stock.xlsx
@@ -15,8 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -61,11 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -431,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1718,6 +1720,256 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>速報ショート型</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>コンビニおにぎりが値下げ（ローソン・セブン・ファミマ）</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>コメ価格の下落を受け、ローソンが手巻きおにぎり20品を9月29日から一律10円値下げ、セブン-イレブンも9月8日から一部おにぎりを232円→213円に値下げ、ファミリーマートも8月25日に「大きなおむすび 昆布とツナマヨネーズ」を320円→298円に値下げすると発表（2026年8月24日報道）。 https://www.jiji.com/jc/article?k=2026082400639&amp;g=eco</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>速報ショート型</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>スーパーの米5kgが平均3191円に下落</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>農水省の週次POSデータによると、2026年8月10日週のスーパーでの米5kg平均販売価格は前週比29円安の3191円となり、新米が出回る前の在庫売り切りや民間在庫量が過去最高水準にあることが要因とされる（2026年8月21日発表）。 https://news.yahoo.co.jp/articles/d26ceeb9300787787bd501ce6a6f811e1488436e</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>速報ショート型</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ローソンが今週の新商品5品を発売</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ローソンが2026年8月25日発売の「今週の新商品」として「キムチ牛カルビ丼」（646円）などホットスナック・グルメ系5商品を発表（2026年8月24日配信）。 https://news.mynavi.jp/article/20260824-4858245/</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>比較(2項目)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>セブンイレブンとローソンの「からあげクン系」商品を100gあたり価格で比較</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>価格・グラム表記が商品パッケージで確認でき、裏取りがしやすい。どちらも定番人気商品でポジティブに紹介しやすい。</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>比較(3項目)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>セブン・ローソン・ファミマの「PB炭酸水500ml」を価格とコスパで比較</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>各社の税込価格・容量が明確で事実確認しやすく、日常的な商品なので視聴者がイメージしやすい。</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>おすすめ〇選</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>業務スーパーの冷凍野菜で毎日の自炊に使えるコスパ優秀アイテム5選</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>価格・内容量が明記されており裏取りが容易。節約というポジティブな切り口で成立する。</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>雑学系</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>コンビニのレジ横ホットスナックにまつわる、知られざる工夫の雑学3選</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>陳列温度管理・調理システム・販売時間帯など複数の雑学ネタを束ねられる広さがあり、ポジティブな豆知識として成立する。</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>単品ディープダイブ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>セブンイレブンの「金の食パン」を価格・原材料・シリーズ展開まで徹底解剖</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>価格や原材料表示は商品パッケージ・公式サイトで裏取り可能。ロングセラー商品でポジティブに掘り下げやすい。</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>定点観測</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>業務スーパーの人気PB「たこ焼き」の価格推移を定点観測</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>過去の購入・レシート記録があれば価格変動を事実ベースで追跡でき、値上げ・据え置きどちらでもニュートラルに報告できる。</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>比較(2項目)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>スーパーと業務スーパーの「切り餅」を1個あたり価格で比較</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>内容量と価格がパッケージ記載で確認しやすく、季節を問わず定番商品でイメージしやすい。</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="E2:E10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">

--- a/channels/food-convenience/research/theme-stock.xlsx
+++ b/channels/food-convenience/research/theme-stock.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1970,6 +1970,256 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>比較(2項目)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>セブンイレブンとファミリーマートのサラダチキンを価格とグラム単価で比較</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>定番の高たんぱく商品で価格・重量とも公式サイトで裏取りしやすく、既存テーマに未登場のカテゴリーのため新鮮に見せられる。</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>比較(2項目)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>スーパーと業務スーパーのレギュラーコーヒー(豆・粉)を100gあたり価格で比較</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>パッケージ表示から価格・内容量を確認しやすく、飲料系だが緑茶や炭酸水とは異なる新規カテゴリーで差別化できる。</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>比較(3項目)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>セブン・ローソン・ファミマのPBカップ麺(定番しょうゆ・みそ系)を価格とスペックで比較</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3社とも公式サイトに価格・内容量が明記されており裏取りが容易で、カップ麺は既存テーマに未登場。</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>比較(3項目)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>スーパー・業務スーパー・コンビニのプレーンヨーグルトを価格と内容量で比較</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>定番の日常食品で価格・グラム数の確認がしやすく、乳製品カテゴリーは牛乳のみ既出のため被りが少ない。</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>おすすめ〇選</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>コンビニで惜しまれつつ販売終了した伝説のスイーツおすすめ5選</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>既存の「おすすめ〇選」がコスパ訴求に偏っているため、話題性・意外性を軸にしたポジティブな懐かしエピソード型でバランスを取る。</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>おすすめ〇選</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>業務スーパーのアレンジ自在な万能調味料・ソースおすすめ5選</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>冷凍食品・お菓子中心だった既存テーマと異なり調味料カテゴリーを扱い、使い方の幅広さという新しい魅力軸を提示できる。</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>雑学系</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>コンビニのコーヒーマシンにまつわる知られざる工夫の雑学3選</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>おにぎりやホットスナックに偏っていた雑学系のカテゴリーを刷新でき、抽出方式や豆の管理など3ネタ以上を束ねられる広さがある。</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>雑学系</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>スーパーの惣菜コーナーにまつわる知られざる不思議3選</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>「知られざる工夫」型に偏りがちな既存傾向に対し、価格変動や陳列タイミングなど理由が明確でない「不思議」型で切り口のバランスを取る。</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>単品ディープダイブ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>マクドナルドの「てりやきマックバーガー」を誕生の経緯と進化の歴史で徹底解剖</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>外食チェーンの看板メニューは対象範囲内で既存テーマと商品が重複せず、日本オリジナル開発という裏話性の高い切り口が使える。</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>定点観測</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>コンビニ各社のPBカップ麺(定番しょうゆ味)の価格を四半期ごとに定点観測</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>既存の定点観測はおにぎりや冷凍食品中心のため、カップ麺という新カテゴリーで価格推移を追うことで切り口を広げられる。</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="E2:E10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">

--- a/channels/food-convenience/research/theme-stock.xlsx
+++ b/channels/food-convenience/research/theme-stock.xlsx
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>台本作成済み</t>
         </is>
       </c>
     </row>
